--- a/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
+++ b/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
@@ -7,42 +7,43 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_BASLANGIC" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_YURUTME_CEKIRDEGI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_KONTROL_LISTESI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_TEKNIK_KAYNAK" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GORSEL_TASARIM" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_MUHASEBE_THP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_KARAR_SATIS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_KAYNAK_HARITASI" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_MODUL_MATRISI" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_YONETISIM_SEVIYESI" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_VERI_SOZLESMELERI" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ANLAM_SOZLESMELERI" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_BAGIMLILIK_HARITASI" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_VARSAYIM_KAYDI" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_FINANSAL_DEGISMEZLER" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_ORACLE_TESTLERI" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_ALTIN_VERI_SETI" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_METAMORFIK_TESTLER" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_HATA_ENJEKSIYONU" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_SISTEM_SAGLIGI" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_VERI_SAGLIGI" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_GUVEN_MOTORU" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_KARAR_KUYRUGU" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_AKSIYON_PLAYBOOK" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_ONAY_AKISI" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_SENARYO_TERS_STRES" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_K3_KULLANICI_TESTI" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_TICARI_DEGER" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_FIYAT_KALITE_KAPISI" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_YAYIN_MANIFESTOSU" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_KANIT_ENVANTERI" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_RELEASE_DURUMU" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_RUNTIME_KOMUTLARI" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_SABITLER_SEMALAR" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_FONKSIYON_ENVANTERI" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_HARDENING_RAPORU" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa1" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_HAKKINDA_VE_REHBER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_YURUTME_CEKIRDEGI" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_KONTROL_LISTESI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_TEKNIK_KAYNAK" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GORSEL_TASARIM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_MUHASEBE_THP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_KARAR_SATIS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_KAYNAK_HARITASI" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_MODUL_MATRISI" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_YONETISIM_SEVIYESI" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_VERI_SOZLESMELERI" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ANLAM_SOZLESMELERI" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_BAGIMLILIK_HARITASI" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_VARSAYIM_KAYDI" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_FINANSAL_DEGISMEZLER" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_ORACLE_TESTLERI" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_ALTIN_VERI_SETI" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_METAMORFIK_TESTLER" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_HATA_ENJEKSIYONU" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_SISTEM_SAGLIGI" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_VERI_SAGLIGI" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_GUVEN_MOTORU" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_KARAR_KUYRUGU" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_AKSIYON_PLAYBOOK" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_ONAY_AKISI" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_SENARYO_TERS_STRES" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_K3_KULLANICI_TESTI" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_TICARI_DEGER" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_FIYAT_KALITE_KAPISI" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_YAYIN_MANIFESTOSU" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_KANIT_ENVANTERI" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_RELEASE_DURUMU" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_RUNTIME_KOMUTLARI" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_SABITLER_SEMALAR" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_FONKSIYON_ENVANTERI" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_HARDENING_RAPORU" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa1" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -52,7 +53,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="27">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -185,8 +186,32 @@
       <color rgb="00047857"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -308,8 +333,26 @@
         <fgColor rgb="FFE7F5EF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -359,11 +402,25 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -529,6 +586,27 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1254,6 +1332,1323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>MODÜL MATRİSİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45.25" customHeight="1">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>v15.1 ALL_MODULES birebir. Her modül Tetikleyici → Girdi → İşlem → Çıktı → Kanıt → Gate → Hata davranışı taşımalıdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Modül</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Tetikleyici</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Girdi</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>İşlem / Algoritma</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Çıktı</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Kanıt Artefaktı</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>Hata / Recovery</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>Durum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>suitability</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Her yeni ürün / yeniden mimari</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Kullanıcı, hacim, eşzamanlılık, IAM, streaming</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Excel uygunluk puanı</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Excel primary / frontend / red</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>SUITABILITY_DECISION.md</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Puan + blocking reason</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Kapsamı daralt / Excel'i SoR diye pazarlama</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Her model</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>6 risk metriği 0–4</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>RiskScore ve T1–T5</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_GOVERNANCE_TIER</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SPEC.md</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Tier kontrolleri tam</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Eksik kontrol → BLOCKED</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>maker_checker</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>T4–T5</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Maker çıktısı + test kanıtı</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Bağımsız checker prosedürü</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Checker raporu</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>CHECKER_REPORT.md; CHECKER_REPORT.csv</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>P0/P1=0</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Checker yoksa final yok</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2+ nesne veya link</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Nesne, olay, ilişki, aksiyon</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Object/Link/Action modelleme</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>ONTOLOGY.csv</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ONTOLOGY.csv</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Orphan=0, duplicate key=0</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Eşleşmiyorsa FAIL</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>data_contracts</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Her input/master/transaction</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Kolon şeması</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Tip/null/enum/range/FK testleri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>DATA_CONTRACTS.csv</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>DATA_CONTRACTS.csv</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Coverage=100%</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Sözleşmesiz input → FAIL</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>semantic_contracts</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Her material KPI</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>KPI iş anlamı + SSOT</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Unit/sign/period/denominator/oracle</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>SEMANTIC_CONTRACTS.csv</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SEMANTIC_CONTRACTS.csv</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Coverage=100%, mismatch=0</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Mismatch → FAIL</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>dependency_graph</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Her workbook</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Formül referansları</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Graph + cycle/fanout/orphan</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>DEPENDENCY_GRAPH.csv</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>DEPENDENCY_GRAPH.csv</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Cycle=0</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Cycle → STOP</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>blast_radius</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Her değişiklik</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>ChangedNode</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Downstream traversal</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Affected tests/reports/decisions</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>DEPENDENCY_GRAPH.csv</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Retest set boş değil</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Retest olmadan release yok</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>financial_identities</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Finansal model</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>BS/CF/Debt/AR/AP vb.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Invariant hesapları</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>INVARIANT_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>INVARIANT_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Tolerance içinde</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Material mismatch → P1 STOP</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>T3+ kritik motor</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>İş kuralı</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Bağımsız yeniden hesaplama</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>ORACLE_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>ORACLE_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>P0/P1 mismatch=0</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Mismatch → STOP</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>golden_dataset</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Her ticari ürün</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>12+ standart vaka</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Versiyonlu beklenen/gerçek</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>GOLDEN_DATASET_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>GOLDEN_DATASET_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Diff=0</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Approved change dışında FAIL</t>
+        </is>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>metamorphic</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Her ticari ürün</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>İlişki testleri</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sıra/duplicate/scenario vb.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>METAMORPHIC_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>METAMORPHIC_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Uygulanabilir testler PASS</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Fail → release yok</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Test kopyası</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Hata enjeksiyonları</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Detection+locator+recovery</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>CHAOS_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>CHAOS_RESULTS.csv; TEST_MATRIX.csv</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Silent corruption=0</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Silent corruption → STOP</t>
+        </is>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>data_observability</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Her veri yükü</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Row/null/duplicate/freshness</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Baseline ve drift</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>DATA_HEALTH</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>DATA_HEALTH.json; DATA_HEALTH.csv</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>SLO threshold</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>StopAge → BLOCKED</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>model_observability</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Her build</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Formula/broken link/recalc/build</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Model telemetry</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>SYSTEM HEALTH</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_HEALTH.json; MODEL_HEALTH.csv</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>SPEC threshold</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Critical failure → BLOCKED</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Karar üreten model</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Source/completeness/freshness/recon/stability</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Ağırlıklı skor + caps</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Confidence score/band</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>CONFIDENCE_RESULTS.json; CONFIDENCE_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Manuel label yok</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Düşük güven → karar bloklanır</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>decision_engine</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Material KPI</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Metric/threshold/confidence/source</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Karar kuralı</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>DECISION_QUEUE</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>DECISION_QUEUE.csv</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Metric valid + confidence yeterli</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>DATA/CONFIDENCE BLOCKED</t>
+        </is>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>playbooks</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>P1/P2 alarm</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Trigger/diagnosis/action</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Playbook</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>ACTION_PLAYBOOKS.csv</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>ACTION_PLAYBOOKS.csv</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>P1 playbook zorunlu</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Eksik P1 playbook → FAIL</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>human_approval</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Yüksek risk/geri döndürülemez</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Durum ve roller</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>State machine</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>APPROVAL_LOG.csv</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>APPROVAL_LOG.csv</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Illegal transition=0</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Onaysız EXECUTED yasak</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>reverse_stress</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>T3+ forecast/investment/credit</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Top 3 driver + kill condition</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Threshold solve</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>REVERSE_STRESS_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>REVERSE_STRESS_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Material decision başına ≥1</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Eksik → FAIL/WARN</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Scenario gereken model</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>ScenarioID/Parent/Assumptions</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Overlay + isolation</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>SCENARIO_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>SCENARIO_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Base unchanged/deterministic</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Source overwrite → FAIL</t>
+        </is>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>k3</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Her ürün</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>5–10 kullanıcı görevi</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Görünür kullanıcı testi</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>K3_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>K3_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Critical tasks=100%</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>GUI yoksa HARİCİ KABUL</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Self-service ürün</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>İlk kullanım görevleri</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Süre ölçümü</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>ONBOARDING_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>ONBOARDING_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>SPEC hedefleri</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Aşılırsa UX yeniden tasarım</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>commercial_value</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Ticari ürün</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Saat/hata/nakit/karar faydası</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>AnnualQuantifiedValue</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>COMMERCIAL_VALUE.json</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>COMMERCIAL_VALUE.json</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>$1000 gate koşulları</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Kanıt yoksa savunulabilir etiketi yok</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>market_validation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Pazar kanıtı iddiası</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Satış/pilot/LOI/interview</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Kanıt doğrulama</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>MARKET_VALIDATION.json</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>MARKET_VALIDATION.json</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Gerçek kanıt</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Yoksa market-proven denmez</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>ooxml_integrity</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Her xlsx release</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>XLSX package</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>ZIP/XML/links/calc scan</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>OOXML_REPORT.json</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>OOXML_REPORT.json</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>Parse/CRC hatası=0</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>Repair/CRC/XML error → FAIL</t>
+        </is>
+      </c>
+      <c r="I30" s="19" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="I5:I30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"BLOCKED,EXTERNAL_ACCEPTANCE_REQUIRED,FAIL,NOT_APPLICABLE,PASS,READY,RUNNING,WARN"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
@@ -1440,7 +2835,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1602,7 +2997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1786,7 +3181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1916,7 +3311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2086,7 +3481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2360,7 +3755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2669,7 +4064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2985,7 +4380,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3230,7 +4625,139 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002563EB"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.5" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="36" customHeight="1">
+      <c r="B2" s="58" t="inlineStr">
+        <is>
+          <t>SİSTEM HAKKINDA, KULLANIM REHBERİ VE TERİMLER SÖZLÜĞÜ (SIEMENS STANDARDI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="B3" s="59" t="inlineStr">
+        <is>
+          <t>5 Yaşındaki Çocuğa Anlatır Gibi Yalın Finansal Karar Mimarisi &amp; Kurumsal Süreç Sözlüğü</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>1. TEMEL MANTIK — 3 DAKİKADA SİSTEMİN ÖZÜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="B7" s="61" t="inlineStr">
+        <is>
+          <t>SORU</t>
+        </is>
+      </c>
+      <c r="C7" s="62" t="inlineStr">
+        <is>
+          <t>GÜNLÜK DİLLE CEVAP (5 YAŞINDA ÇOCUĞA ANLATIR GİBİ)</t>
+        </is>
+      </c>
+      <c r="D7" s="62" t="inlineStr">
+        <is>
+          <t>ŞİRKETİNİZE FAYDASI NE?</t>
+        </is>
+      </c>
+      <c r="E7" s="61" t="inlineStr">
+        <is>
+          <t>İLGİLİ SAYFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="B8" s="63" t="inlineStr">
+        <is>
+          <t>1. Bu dosya ne işe yarar?</t>
+        </is>
+      </c>
+      <c r="C8" s="64" t="inlineStr">
+        <is>
+          <t>Tıpkı bir uçağın kokpiti gibidir. Şirketin tüm borçlarını, taksitlerini ve kasadaki parasını tek bakışta gösterir.</t>
+        </is>
+      </c>
+      <c r="D8" s="64" t="inlineStr">
+        <is>
+          <t>Gözden kaçan taksitleri sıfırlar; faiz cezası ve itibar kaybını önler.</t>
+        </is>
+      </c>
+      <c r="E8" s="63" t="inlineStr">
+        <is>
+          <t>PANO, YÖNETİM_RAPORU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="B9" s="65" t="inlineStr">
+        <is>
+          <t>2. Kullanıcı olarak ben ne yapacağım?</t>
+        </is>
+      </c>
+      <c r="C9" s="66" t="inlineStr">
+        <is>
+          <t>Yalnızca 'GİRDİLER' sekmesindeki sarı renkli hücrelere kredilerinizi yazacaksınız. Geri kalan her şeyi robot hesaplar.</t>
+        </is>
+      </c>
+      <c r="D9" s="66" t="inlineStr">
+        <is>
+          <t>Veri girişi 5 dakikada biter; karmaşık formüllerle veya kodlarla uğraşmazsınız.</t>
+        </is>
+      </c>
+      <c r="E9" s="65" t="inlineStr">
+        <is>
+          <t>GİRDİLER, KREDILER</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="B10" s="63" t="inlineStr">
+        <is>
+          <t>3. Sistem bana ne kazandırır?</t>
+        </is>
+      </c>
+      <c r="C10" s="64" t="inlineStr">
+        <is>
+          <t>Hangi bankanın pahalı olduğunu tespit eder. Borcu ucuza taşıyarak şirketinize somut nakit kazandırır.</t>
+        </is>
+      </c>
+      <c r="D10" s="64" t="inlineStr">
+        <is>
+          <t>Gereksiz faiz ve komisyonları yok eder; banka pazarlıklarında şirketinizi güçlü kılar.</t>
+        </is>
+      </c>
+      <c r="E10" s="63" t="inlineStr">
+        <is>
+          <t>REFINANSMAN, KARAR_MOTORU</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3545,506 +5072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="46" t="inlineStr">
-        <is>
-          <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="1" t="n"/>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Adım</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Modül</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Tetikleyici</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Zorunlu Kanıt</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>GEÇTİ Kuralı</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Hata Durumu</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Sonraki Aşama</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Excel Uygunluğu</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Her yeni model</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>UYGUNLUK_KARARI</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Excel'in rolü açık</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>HATA / BLOKE</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Yönetişim</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Yönetişim</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Her model</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Risk seviyesi + etki girdileri</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Seviye hesaplandı</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>BLOKE</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Sözleşmeler</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Türk Muhasebe Eşlemesi</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Finansal model</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>THP hesap eşleme tablosu</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Kritik satırlar THP ile uyumlu</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Sözleşmeler</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Veri ve Anlam Sözleşmeleri</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Girdi/KPI varsa</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Veri + KPI sözleşmeleri</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Kapsam %100</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Üretim</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Üretim</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Sözleşmeler GEÇTİ</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Çalışan Excel</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Tek gerçek kaynak korunmuş</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Testler</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Görsel/Kullanım Katmanı</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Motor hazır</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Başlıklar + renk + grafik + yönlendirme</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Tüm kullanıcı sayfaları standarda uygun</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Testler</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Testler</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Üretim tamam</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Formül/OOXML/kimlik/oracle/golden/metamorfik</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Uygulanabilir hard gate'ler GEÇTİ</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Kanıt</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Hata-Kontrol Tutarlılığı</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Test sonucu var</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Hata taraması + kontrol sonuçları</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Formül hatası varken GEÇTİ yok</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Kanıt</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Kanıt</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Test sonucu var</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Makine okunur artefakt + özet</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Kanıt fiziksel ve tutarlı</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Kullanıcı Kabulü</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Kullanıcı Kabulü</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Kritik görevler</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Gerçek ekran davranışı</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Kritik görevler %100</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>DIŞ_KABUL_GEREKLİ</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Ticari</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Ticari Değer</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Ürün satılacaksa</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>ROI + demo + kanıt paketi</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Ekonomik değer kanıtlı</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>UYARI / HATA</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Pazar Doğrulama</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Pazar Doğrulama</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Pazar iddiası varsa</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Ücretli satış/pilot/fiyat kabul kanıtı</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Gerçek fiyat kabul kanıtı</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>UYGULANMAZ / HATA</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Yayın</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4249,7 +5277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4439,7 +5467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4643,7 +5671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4803,7 +5831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4931,7 +5959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5145,7 +6173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5281,7 +6309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5570,7 +6598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5810,7 +6838,506 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="46" t="inlineStr">
+        <is>
+          <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Adım</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Modül</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Tetikleyici</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Zorunlu Kanıt</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>GEÇTİ Kuralı</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Hata Durumu</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Sonraki Aşama</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Excel Uygunluğu</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Her yeni model</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>UYGUNLUK_KARARI</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Excel'in rolü açık</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>HATA / BLOKE</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Yönetişim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Yönetişim</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Her model</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Risk seviyesi + etki girdileri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Seviye hesaplandı</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Sözleşmeler</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Türk Muhasebe Eşlemesi</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Finansal model</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>THP hesap eşleme tablosu</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Kritik satırlar THP ile uyumlu</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Sözleşmeler</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Veri ve Anlam Sözleşmeleri</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Girdi/KPI varsa</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Veri + KPI sözleşmeleri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Kapsam %100</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Üretim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Üretim</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Sözleşmeler GEÇTİ</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Çalışan Excel</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Tek gerçek kaynak korunmuş</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Testler</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Görsel/Kullanım Katmanı</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Motor hazır</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Başlıklar + renk + grafik + yönlendirme</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Tüm kullanıcı sayfaları standarda uygun</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Testler</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Testler</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Üretim tamam</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Formül/OOXML/kimlik/oracle/golden/metamorfik</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Uygulanabilir hard gate'ler GEÇTİ</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Kanıt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Hata-Kontrol Tutarlılığı</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Test sonucu var</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Hata taraması + kontrol sonuçları</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Formül hatası varken GEÇTİ yok</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Kanıt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Kanıt</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Test sonucu var</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Makine okunur artefakt + özet</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Kanıt fiziksel ve tutarlı</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Kullanıcı Kabulü</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Kullanıcı Kabulü</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Kritik görevler</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Gerçek ekran davranışı</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Kritik görevler %100</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>DIŞ_KABUL_GEREKLİ</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Ticari</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Ticari Değer</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Ürün satılacaksa</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>ROI + demo + kanıt paketi</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Ekonomik değer kanıtlı</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>UYARI / HATA</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Pazar Doğrulama</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Pazar Doğrulama</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Pazar iddiası varsa</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Ücretli satış/pilot/fiyat kabul kanıtı</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Gerçek fiyat kabul kanıtı</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>UYGULANMAZ / HATA</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Yayın</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6009,7 +7536,2293 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="72" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>YAYIN MANİFESTOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45.25" customHeight="1">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>Python RELEASE_MANIFEST şemasının Excel-native görünümü.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Değer</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Kaynak / Kanıt</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Durum</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>Paket Bileşeni</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>Dosya / Hash</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>MASTER Standart</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>suite_version</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Runtime Kernel</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Runtime SHA-256</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>babe066ab599199123e53d01944bcd9d75648a579ade69ab9303dd675962f481</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>build_id</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>generated_at_utc</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>governance_tier</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>compatibility_profile</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>hard_failures</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>release_status</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5:D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"BLOCKED,EXTERNAL_ACCEPTANCE_REQUIRED,FAIL,NOT_APPLICABLE,PASS,READY,RUNNING,WARN"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>KANIT ENVANTERİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45.25" customHeight="1">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>PASS yalnız fiziksel/ölçülebilir kanıtla mümkündür. Hash release kanıt zincirini güçlendirir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Artefakt</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Zorunlu mu?</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Kaynak Modül</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>SHA-256 / Referans</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Son Doğrulama</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Durum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ASSUMPTION_REGISTER.csv</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CHANGELOG.md</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CONTROL_CATALOG.csv</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>DATA_CONTRACTS.csv</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>data_contracts</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>DEPENDENCY_GRAPH.csv</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>dependency_graph</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>GOLDEN_DATASET_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>golden_dataset</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ONTOLOGY.csv</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ORACLE_RESULTS.csv</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>RELEASE_MANIFEST.json</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>RELEASE_REPORT.md</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ROLLBACK_PLAN.md</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>SEMANTIC_CONTRACTS.csv</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>semantic_contracts</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>SPEC.md</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TEST_MATRIX.csv</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>VALUE_MAP.md</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F5:F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"BLOCKED,EXTERNAL_ACCEPTANCE_REQUIRED,FAIL,NOT_APPLICABLE,PASS,READY,RUNNING,WARN"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>RELEASE DURUM MAKİNESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45.25" customHeight="1">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>Python RELEASE_STATES ve fail-closed mantığı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Sıra</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Release Durumu</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Giriş Koşulu</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Final Anlamı</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>TASLAK (DRAFT)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Eksik/blocked modül olabilir</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Yayın değil</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>MÜHENDİSLİK_GEÇTİ</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Engineering hard gates PASS</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Teknik çekirdek geçti</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>FİNANS_GEÇTİ</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Financial identities/oracle gerekli yerde PASS</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Finansal çekirdek geçti</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>KULLANICI_KABULÜ_GEREKLİ</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>K3 için Excel GUI/harici kabul gerekiyor</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>FINAL değil</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>TİCARİ_SAVUNULABİLİR</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Commercial value gate PASS</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Pazarın ödeyeceği kanıtlanmış değildir</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>PAZAR_DOĞRULANDI</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Ücretli satış/pilot/LOI/fiyat kabul kanıtı</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>WTP kanıtı var</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>NİHAİ_YAYIN</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Tüm uygulanabilir hard gates PASS</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Teknik/finansal release tamam</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>PYTHON RUNTIME KOMUTLARI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45.25" customHeight="1">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>Kaynak kernelin desteklediği komutlar. Excel tek kaynak olsa da runtime davranışı burada korunur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Amaç</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Komut</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Mandate yazdır</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --print-mandate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Mandate çıkar</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --extract-mandate out.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Hardening raporu</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --print-hardening-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Proje başlat</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --init-project &lt;dir&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline çalıştır</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --run &lt;project_dir&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Manifest doğrula</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --verify RELEASE_MANIFEST.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>XLSX tara</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --scan-xlsx workbook.xlsx</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>SABİTLER VE ŞEMALAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45.25" customHeight="1">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>Kernel sabitleri ve makine-okunur sözleşmelerin tek görünümü.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Sabit</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Değer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SUITE_VERSION</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>15.1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>KERNEL_NAME</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>EXCELARSIV_DECISION_OS_HARDENED_KERNEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ALLOWED_STATUSES</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>PASS | READY | BLOCKED | FAIL | RUNNING | EXTERNAL_ACCEPTANCE_REQUIRED | NOT_APPLICABLE | WARN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>HARD_PASS</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE | PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>RELEASE_STATES</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>FINAL_RELEASE | ENGINEERING_PASS | UAT_REQUIRED | DRAFT | COMMERCIAL_DEFENSIBLE | MARKET_VALIDATED | FINANCIAL_PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ALL_MODULES</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>suitability | governance | maker_checker | ontology | data_contracts | semantic_contracts | dependency_graph | blast_radius | financial_identities | oracle | golden_dataset | metamorphic | chaos | data_observability | model_observability | confidence | decision_engine | playbooks | human_approval | reverse_stress | scenario | k3 | onboarding | commercial_value | market_validation | ooxml_integrity</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>CORE_ARTIFACTS</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>RELEASE_REPORT.md | CONTROL_CATALOG.csv | DEPENDENCY_GRAPH.csv | GOLDEN_DATASET_RESULTS.csv | CHANGELOG.md | ROLLBACK_PLAN.md | ASSUMPTION_REGISTER.csv | SPEC.md | ONTOLOGY.csv | SEMANTIC_CONTRACTS.csv | VALUE_MAP.md | ORACLE_RESULTS.csv | TEST_MATRIX.csv | DATA_CONTRACTS.csv | RELEASE_MANIFEST.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="68" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>PYTHON FONKSİYON ENVANTERİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45.25" customHeight="1">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>Kerneldeki tüm fonksiyonlar, satır aralıkları ve sorumlulukları.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Fonksiyon</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Başlangıç Satırı</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Bitiş Satırı</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Argümanlar</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Açıklama</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>_utc_now</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>6548</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>6549</v>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Yardımcı</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>_read_json</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>6552</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>6553</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Yardımcı</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>_write_json</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>6556</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>6557</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>path, data</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Yardımcı</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>_sha256_file</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>6560</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>6565</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Yardımcı</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>_csv_rows</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>6568</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>6571</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Yardımcı</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>_normalize_bool</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>6574</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>6577</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Yardımcı</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>_num</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>6580</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>6586</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>v, default</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Yardımcı</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>run_suitability_engine</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>6591</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>6630</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>cfg</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Çalışan Motor</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>run_governance_engine</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>6633</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>6643</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>cfg</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Çalışan Motor</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>run_confidence_engine</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>6646</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>6666</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>cfg</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Çalışan Motor</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>run_commercial_value_engine</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>6669</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>6698</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>cfg</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Çalışan Motor</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>required_modules_for_tier</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>6701</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>6718</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>tier, cfg</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Yardımcı</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>validate_csv_schema</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>6723</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>6736</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>path, required_columns</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Doğrulama / Gate</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>validate_dependency_graph</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>6739</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>6767</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Doğrulama / Gate</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>validate_result_csv</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>6770</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>6784</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>path, result_column</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Doğrulama / Gate</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>validate_artifact_set</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>6787</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>6809</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>project_dir, tier, include_manifest</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Doğrulama / Gate</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>scan_ooxml</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>6812</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>6854</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>workbook_path</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Doğrulama / Gate</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>_resolve_evidence</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>6859</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>6869</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>project_dir, evidence</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Yardımcı</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>verify_manifest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>6872</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>6975</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>path, strict</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Doğrulama / Gate</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>_render_suitability_md</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>6980</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>6986</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Yardımcı</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>run_pipeline</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6989</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>7077</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>project_dir</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Çalışan Motor</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>init_project</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>7080</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>7122</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>project_dir</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline / CLI</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>print_usage</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>7169</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>7183</v>
+      </c>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Yardımcı</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>7186</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>7240</v>
+      </c>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>Pipeline / CLI</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>v15.1 HARDENING RAPORU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45.25" customHeight="1">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>Python HARDENING_REPORT içeriğinin tek kaynak Excel'deki okunabilir kopyası.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Satır</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t># EXCELARŞİV V15 HARDENING REPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>## Release</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>- Kernel: EXCELARSIV_DECISION_OS_HARDENED_KERNEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>- Suite: 15.1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>- Base: EXCELARSIV_V15_UNIFIED_SUITE.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>## Structural upgrades</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>1. Tier-aware required module matrix (T1-T5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>2. Evidence path validation with project-root confinement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>3. SHA-256 evidence hashing for release artifacts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>4. Strict release-state whitelist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>5. FINAL_RELEASE requires PASS / NOT_APPLICABLE only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>6. K3 EXTERNAL_ACCEPTANCE_REQUIRED blocks FINAL_RELEASE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>7. Maker/checker, reverse-stress, scenario, onboarding, human approval and OOXML added to module graph.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>8. Spreadsheet Suitability Engine is executable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>9. Governance Tier Engine is executable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>10. Confidence Engine is executable with hard caps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>11. Commercial Value Engine is executable and separates economic defensibility from market validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>12. CSV contract/schema validator added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>13. Dependency graph cycle detector added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>14. Result-table PASS enforcement added for Oracle, Golden Dataset, Metamorphic and Invariants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>15. OOXML ZIP/XML integrity scanner added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>16. Pipeline is fail-closed: missing runtime evidence becomes BLOCKED / DRAFT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>## Runtime proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>- Python compilation: PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>- Empty initialized project: correctly remains DRAFT and fails closed because mandatory evidence is missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>- Existing KILIC workbook OOXML scan:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>- ZIP integrity: PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>- XML parse errors: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>- external links: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>- sheet XML count: 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>- formula count: 101,946</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>- calcMode: auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>- fullCalcOnLoad: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>- forceFullCalc: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>## Important boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>This kernel does not claim to reproduce Palantir Gotham, Primer AI or Recorded Future. It adopts public architectural mechanisms such as ontology/object-link-action modeling, evidence lineage, confidence-aware decisioning, workflow state/error handling and governance. Excel remains bounded by Excel's runtime, security, concurrency and recalculation limits.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6802,2293 +10615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="72" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
-        <is>
-          <t>YAYIN MANİFESTOSU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45.25" customHeight="1">
-      <c r="A2" s="57" t="inlineStr">
-        <is>
-          <t>Python RELEASE_MANIFEST şemasının Excel-native görünümü.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Alan</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Kaynak / Kanıt</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Durum</t>
-        </is>
-      </c>
-      <c r="F4" s="29" t="inlineStr">
-        <is>
-          <t>Paket Bileşeni</t>
-        </is>
-      </c>
-      <c r="G4" s="29" t="inlineStr">
-        <is>
-          <t>Dosya / Hash</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>schema_version</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>MASTER Standart</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>suite_version</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Runtime Kernel</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>kernel</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Runtime SHA-256</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>babe066ab599199123e53d01944bcd9d75648a579ade69ab9303dd675962f481</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>build_id</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>generated_at_utc</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>governance_tier</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>compatibility_profile</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>hard_failures</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>release_status</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="D5:D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"BLOCKED,EXTERNAL_ACCEPTANCE_REQUIRED,FAIL,NOT_APPLICABLE,PASS,READY,RUNNING,WARN"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="66" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
-        <is>
-          <t>KANIT ENVANTERİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45.25" customHeight="1">
-      <c r="A2" s="57" t="inlineStr">
-        <is>
-          <t>PASS yalnız fiziksel/ölçülebilir kanıtla mümkündür. Hash release kanıt zincirini güçlendirir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Artefakt</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Zorunlu mu?</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Kaynak Modül</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>SHA-256 / Referans</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>Son Doğrulama</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>Durum</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMPTION_REGISTER.csv</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>CHANGELOG.md</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>CONTROL_CATALOG.csv</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>DATA_CONTRACTS.csv</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>data_contracts</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>DEPENDENCY_GRAPH.csv</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>dependency_graph</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>GOLDEN_DATASET_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>golden_dataset</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>ONTOLOGY.csv</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>ontology</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>ORACLE_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>oracle</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>RELEASE_MANIFEST.json</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>RELEASE_REPORT.md</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>ROLLBACK_PLAN.md</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>SEMANTIC_CONTRACTS.csv</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>semantic_contracts</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>SPEC.md</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>governance</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>TEST_MATRIX.csv</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>chaos</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>VALUE_MAP.md</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Evet</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F5:F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"BLOCKED,EXTERNAL_ACCEPTANCE_REQUIRED,FAIL,NOT_APPLICABLE,PASS,READY,RUNNING,WARN"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
-        <is>
-          <t>RELEASE DURUM MAKİNESİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45.25" customHeight="1">
-      <c r="A2" s="57" t="inlineStr">
-        <is>
-          <t>Python RELEASE_STATES ve fail-closed mantığı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Sıra</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Release Durumu</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Giriş Koşulu</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Final Anlamı</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>TASLAK (DRAFT)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Eksik/blocked modül olabilir</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Yayın değil</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>MÜHENDİSLİK_GEÇTİ</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Engineering hard gates PASS</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>Teknik çekirdek geçti</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>FİNANS_GEÇTİ</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Financial identities/oracle gerekli yerde PASS</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Finansal çekirdek geçti</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>KULLANICI_KABULÜ_GEREKLİ</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>K3 için Excel GUI/harici kabul gerekiyor</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>FINAL değil</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>TİCARİ_SAVUNULABİLİR</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Commercial value gate PASS</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Pazarın ödeyeceği kanıtlanmış değildir</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>PAZAR_DOĞRULANDI</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Ücretli satış/pilot/LOI/fiyat kabul kanıtı</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>WTP kanıtı var</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>NİHAİ_YAYIN</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>Tüm uygulanabilir hard gates PASS</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>Teknik/finansal release tamam</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="92" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
-        <is>
-          <t>PYTHON RUNTIME KOMUTLARI</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45.25" customHeight="1">
-      <c r="A2" s="57" t="inlineStr">
-        <is>
-          <t>Kaynak kernelin desteklediği komutlar. Excel tek kaynak olsa da runtime davranışı burada korunur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Amaç</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Komut</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Mandate yazdır</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --print-mandate</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Mandate çıkar</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --extract-mandate out.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Hardening raporu</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --print-hardening-report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Proje başlat</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --init-project &lt;dir&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Pipeline çalıştır</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --run &lt;project_dir&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Manifest doğrula</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --verify RELEASE_MANIFEST.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>XLSX tara</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>python EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py --scan-xlsx workbook.xlsx</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
-        <is>
-          <t>SABİTLER VE ŞEMALAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45.25" customHeight="1">
-      <c r="A2" s="57" t="inlineStr">
-        <is>
-          <t>Kernel sabitleri ve makine-okunur sözleşmelerin tek görünümü.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Sabit</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>SUITE_VERSION</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>15.1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>KERNEL_NAME</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>EXCELARSIV_DECISION_OS_HARDENED_KERNEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>ALLOWED_STATUSES</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>PASS | READY | BLOCKED | FAIL | RUNNING | EXTERNAL_ACCEPTANCE_REQUIRED | NOT_APPLICABLE | WARN</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>HARD_PASS</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE | PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>RELEASE_STATES</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>FINAL_RELEASE | ENGINEERING_PASS | UAT_REQUIRED | DRAFT | COMMERCIAL_DEFENSIBLE | MARKET_VALIDATED | FINANCIAL_PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>ALL_MODULES</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>suitability | governance | maker_checker | ontology | data_contracts | semantic_contracts | dependency_graph | blast_radius | financial_identities | oracle | golden_dataset | metamorphic | chaos | data_observability | model_observability | confidence | decision_engine | playbooks | human_approval | reverse_stress | scenario | k3 | onboarding | commercial_value | market_validation | ooxml_integrity</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>CORE_ARTIFACTS</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>RELEASE_REPORT.md | CONTROL_CATALOG.csv | DEPENDENCY_GRAPH.csv | GOLDEN_DATASET_RESULTS.csv | CHANGELOG.md | ROLLBACK_PLAN.md | ASSUMPTION_REGISTER.csv | SPEC.md | ONTOLOGY.csv | SEMANTIC_CONTRACTS.csv | VALUE_MAP.md | ORACLE_RESULTS.csv | TEST_MATRIX.csv | DATA_CONTRACTS.csv | RELEASE_MANIFEST.json</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="68" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
-        <is>
-          <t>PYTHON FONKSİYON ENVANTERİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45.25" customHeight="1">
-      <c r="A2" s="57" t="inlineStr">
-        <is>
-          <t>Kerneldeki tüm fonksiyonlar, satır aralıkları ve sorumlulukları.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Fonksiyon</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Başlangıç Satırı</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Bitiş Satırı</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Argümanlar</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>Açıklama</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>_utc_now</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>6548</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>6549</v>
-      </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Yardımcı</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>_read_json</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>6552</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>6553</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>path</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Yardımcı</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>_write_json</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>6556</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>6557</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>path, data</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Yardımcı</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>_sha256_file</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>6560</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>6565</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>path</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Yardımcı</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>_csv_rows</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>6568</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>6571</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>path</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Yardımcı</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>_normalize_bool</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>6574</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>6577</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>v</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Yardımcı</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>_num</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>6580</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>6586</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>v, default</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Yardımcı</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>run_suitability_engine</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>6591</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>6630</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>cfg</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Çalışan Motor</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>run_governance_engine</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>6633</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>6643</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>cfg</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Çalışan Motor</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>run_confidence_engine</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>6646</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>6666</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>cfg</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Çalışan Motor</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>run_commercial_value_engine</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>6669</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>6698</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>cfg</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Çalışan Motor</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>required_modules_for_tier</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>6701</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>6718</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>tier, cfg</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Yardımcı</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>validate_csv_schema</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>6723</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>6736</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>path, required_columns</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Doğrulama / Gate</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>validate_dependency_graph</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>6739</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>6767</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>path</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Doğrulama / Gate</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>validate_result_csv</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>6770</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>6784</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>path, result_column</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Doğrulama / Gate</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>validate_artifact_set</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>6787</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>6809</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>project_dir, tier, include_manifest</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Doğrulama / Gate</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>scan_ooxml</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>6812</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>6854</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>workbook_path</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Doğrulama / Gate</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>_resolve_evidence</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>6859</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>6869</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>project_dir, evidence</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Yardımcı</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>verify_manifest</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>6872</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>6975</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>path, strict</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Doğrulama / Gate</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>_render_suitability_md</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>6980</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>6986</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Yardımcı</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>run_pipeline</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>6989</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>7077</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>project_dir</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Çalışan Motor</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>init_project</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>7080</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>7122</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>project_dir</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Pipeline / CLI</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>print_usage</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>7169</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>7183</v>
-      </c>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Yardımcı</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="n">
-        <v>7186</v>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>7240</v>
-      </c>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>Pipeline / CLI</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>Kaynak kod satırları 99_TEKNIK_KAYNAK sayfasında.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
-        <is>
-          <t>v15.1 HARDENING RAPORU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45.25" customHeight="1">
-      <c r="A2" s="57" t="inlineStr">
-        <is>
-          <t>Python HARDENING_REPORT içeriğinin tek kaynak Excel'deki okunabilir kopyası.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Satır</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>İçerik</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t># EXCELARŞİV V15 HARDENING REPORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>## Release</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>- Kernel: EXCELARSIV_DECISION_OS_HARDENED_KERNEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>- Suite: 15.1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>- Base: EXCELARSIV_V15_UNIFIED_SUITE.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>## Structural upgrades</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>1. Tier-aware required module matrix (T1-T5).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>2. Evidence path validation with project-root confinement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>3. SHA-256 evidence hashing for release artifacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>4. Strict release-state whitelist.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>5. FINAL_RELEASE requires PASS / NOT_APPLICABLE only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>6. K3 EXTERNAL_ACCEPTANCE_REQUIRED blocks FINAL_RELEASE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>7. Maker/checker, reverse-stress, scenario, onboarding, human approval and OOXML added to module graph.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>8. Spreadsheet Suitability Engine is executable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>9. Governance Tier Engine is executable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>10. Confidence Engine is executable with hard caps.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>11. Commercial Value Engine is executable and separates economic defensibility from market validation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>12. CSV contract/schema validator added.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>13. Dependency graph cycle detector added.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>14. Result-table PASS enforcement added for Oracle, Golden Dataset, Metamorphic and Invariants.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>15. OOXML ZIP/XML integrity scanner added.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>16. Pipeline is fail-closed: missing runtime evidence becomes BLOCKED / DRAFT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>## Runtime proof</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>- Python compilation: PASS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>- Empty initialized project: correctly remains DRAFT and fails closed because mandatory evidence is missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>- Existing KILIC workbook OOXML scan:</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>- ZIP integrity: PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>- XML parse errors: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>- external links: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>- sheet XML count: 15</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>- formula count: 101,946</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>- calcMode: auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>- fullCalcOnLoad: 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>- forceFullCalc: 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>## Important boundary</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="18" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>This kernel does not claim to reproduce Palantir Gotham, Primer AI or Recorded Future. It adopts public architectural mechanisms such as ontology/object-link-action modeling, evidence lineage, confidence-aware decisioning, workflow state/error handling and governance. Excel remains bounded by Excel's runtime, security, concurrency and recalculation limits.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38138,13 +39665,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38909,6 +40436,23 @@
       <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Varsayılan 8.43 genişliği / dar kolonlar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Siemens &amp; Enterprise UI Standartı</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>00_HAKKINDA_VE_REHBER (5 yaşındaki çocuğa anlatır gibi sistem sözlüğü), kart içi sıfır gridline/artık border, simetrik dış çerçeve ve altın oran sütun genişlikleri zorunludur.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ZORUNLU</t>
         </is>
       </c>
     </row>
@@ -38928,7 +40472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39472,7 +41016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40047,7 +41591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44587,1321 +46131,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
-        <is>
-          <t>MODÜL MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45.25" customHeight="1">
-      <c r="A2" s="57" t="inlineStr">
-        <is>
-          <t>v15.1 ALL_MODULES birebir. Her modül Tetikleyici → Girdi → İşlem → Çıktı → Kanıt → Gate → Hata davranışı taşımalıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Modül</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Tetikleyici</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Girdi</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>İşlem / Algoritma</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>Çıktı</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>Kanıt Artefaktı</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="H4" s="16" t="inlineStr">
-        <is>
-          <t>Hata / Recovery</t>
-        </is>
-      </c>
-      <c r="I4" s="16" t="inlineStr">
-        <is>
-          <t>Durum</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>suitability</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Her yeni ürün / yeniden mimari</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Kullanıcı, hacim, eşzamanlılık, IAM, streaming</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Excel uygunluk puanı</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Excel primary / frontend / red</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>SUITABILITY_DECISION.md</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Puan + blocking reason</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Kapsamı daralt / Excel'i SoR diye pazarlama</t>
-        </is>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>governance</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Her model</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>6 risk metriği 0–4</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>RiskScore ve T1–T5</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>MODEL_GOVERNANCE_TIER</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>SPEC.md</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Tier kontrolleri tam</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Eksik kontrol → BLOCKED</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>maker_checker</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>T4–T5</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Maker çıktısı + test kanıtı</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Bağımsız checker prosedürü</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Checker raporu</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>CHECKER_REPORT.md; CHECKER_REPORT.csv</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>P0/P1=0</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Checker yoksa final yok</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>ontology</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>2+ nesne veya link</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Nesne, olay, ilişki, aksiyon</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Object/Link/Action modelleme</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ONTOLOGY.csv</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>ONTOLOGY.csv</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Orphan=0, duplicate key=0</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Eşleşmiyorsa FAIL</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>data_contracts</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Her input/master/transaction</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Kolon şeması</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Tip/null/enum/range/FK testleri</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>DATA_CONTRACTS.csv</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>DATA_CONTRACTS.csv</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Coverage=100%</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Sözleşmesiz input → FAIL</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>semantic_contracts</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Her material KPI</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>KPI iş anlamı + SSOT</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Unit/sign/period/denominator/oracle</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>SEMANTIC_CONTRACTS.csv</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>SEMANTIC_CONTRACTS.csv</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Coverage=100%, mismatch=0</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Mismatch → FAIL</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>dependency_graph</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Her workbook</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Formül referansları</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Graph + cycle/fanout/orphan</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>DEPENDENCY_GRAPH.csv</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>DEPENDENCY_GRAPH.csv</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Cycle=0</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Cycle → STOP</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>blast_radius</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Her değişiklik</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>ChangedNode</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Downstream traversal</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Affected tests/reports/decisions</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>DEPENDENCY_GRAPH.csv</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Retest set boş değil</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Retest olmadan release yok</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>financial_identities</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Finansal model</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>BS/CF/Debt/AR/AP vb.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Invariant hesapları</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>INVARIANT_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>INVARIANT_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Tolerance içinde</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Material mismatch → P1 STOP</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>oracle</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>T3+ kritik motor</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>İş kuralı</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Bağımsız yeniden hesaplama</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>ORACLE_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>ORACLE_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>P0/P1 mismatch=0</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Mismatch → STOP</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>golden_dataset</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Her ticari ürün</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>12+ standart vaka</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Versiyonlu beklenen/gerçek</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>GOLDEN_DATASET_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>GOLDEN_DATASET_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Diff=0</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Approved change dışında FAIL</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>metamorphic</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Her ticari ürün</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>İlişki testleri</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Sıra/duplicate/scenario vb.</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>METAMORPHIC_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>METAMORPHIC_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Uygulanabilir testler PASS</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Fail → release yok</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>chaos</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Test kopyası</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Hata enjeksiyonları</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Detection+locator+recovery</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>CHAOS_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>CHAOS_RESULTS.csv; TEST_MATRIX.csv</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Silent corruption=0</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Silent corruption → STOP</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>data_observability</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Her veri yükü</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Row/null/duplicate/freshness</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Baseline ve drift</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>DATA_HEALTH</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>DATA_HEALTH.json; DATA_HEALTH.csv</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>SLO threshold</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>StopAge → BLOCKED</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>model_observability</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Her build</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Formula/broken link/recalc/build</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Model telemetry</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>SYSTEM HEALTH</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>MODEL_HEALTH.json; MODEL_HEALTH.csv</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>SPEC threshold</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Critical failure → BLOCKED</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Karar üreten model</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Source/completeness/freshness/recon/stability</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Ağırlıklı skor + caps</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Confidence score/band</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_RESULTS.json; CONFIDENCE_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Manuel label yok</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Düşük güven → karar bloklanır</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>decision_engine</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Material KPI</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Metric/threshold/confidence/source</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Karar kuralı</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>DECISION_QUEUE</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>DECISION_QUEUE.csv</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Metric valid + confidence yeterli</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>DATA/CONFIDENCE BLOCKED</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>playbooks</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>P1/P2 alarm</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Trigger/diagnosis/action</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Playbook</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>ACTION_PLAYBOOKS.csv</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>ACTION_PLAYBOOKS.csv</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>P1 playbook zorunlu</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Eksik P1 playbook → FAIL</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>human_approval</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Yüksek risk/geri döndürülemez</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Durum ve roller</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>State machine</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>APPROVAL_LOG.csv</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>APPROVAL_LOG.csv</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Illegal transition=0</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Onaysız EXECUTED yasak</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>reverse_stress</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>T3+ forecast/investment/credit</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Top 3 driver + kill condition</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Threshold solve</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>REVERSE_STRESS_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>REVERSE_STRESS_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Material decision başına ≥1</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Eksik → FAIL/WARN</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Scenario gereken model</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>ScenarioID/Parent/Assumptions</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Overlay + isolation</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>SCENARIO_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>SCENARIO_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Base unchanged/deterministic</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Source overwrite → FAIL</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>k3</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Her ürün</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>5–10 kullanıcı görevi</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Görünür kullanıcı testi</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>K3_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>K3_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Critical tasks=100%</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>GUI yoksa HARİCİ KABUL</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>onboarding</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Self-service ürün</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>İlk kullanım görevleri</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Süre ölçümü</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>ONBOARDING_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>ONBOARDING_RESULTS.csv</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>SPEC hedefleri</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Aşılırsa UX yeniden tasarım</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>commercial_value</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Ticari ürün</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Saat/hata/nakit/karar faydası</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>AnnualQuantifiedValue</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>COMMERCIAL_VALUE.json</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>COMMERCIAL_VALUE.json</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>$1000 gate koşulları</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Kanıt yoksa savunulabilir etiketi yok</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>market_validation</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Pazar kanıtı iddiası</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Satış/pilot/LOI/interview</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Kanıt doğrulama</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>MARKET_VALIDATION.json</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>MARKET_VALIDATION.json</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Gerçek kanıt</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Yoksa market-proven denmez</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>ooxml_integrity</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>Her xlsx release</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>XLSX package</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>ZIP/XML/links/calc scan</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>OOXML_REPORT.json</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>OOXML_REPORT.json</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>Parse/CRC hatası=0</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="inlineStr">
-        <is>
-          <t>Repair/CRC/XML error → FAIL</t>
-        </is>
-      </c>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="I5:I30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"BLOCKED,EXTERNAL_ACCEPTANCE_REQUIRED,FAIL,NOT_APPLICABLE,PASS,READY,RUNNING,WARN"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
+++ b/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
@@ -420,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -607,6 +607,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -940,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -948,7 +966,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
@@ -1320,7 +1338,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6844,7 +6862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6857,7 +6875,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
@@ -9828,7 +9846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9838,7 +9856,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
@@ -10593,7 +10611,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E29">
     <cfRule type="expression" priority="1" dxfId="1">
@@ -39671,7 +39689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39683,7 +39701,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="70" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
@@ -40451,6 +40469,23 @@
         </is>
       </c>
       <c r="D28" t="inlineStr">
+        <is>
+          <t>ZORUNLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sıfır Metin Kırılması (Zero Subtitle Wrap)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tüm sayfalarda A1 (Banner) ve A3 (Açıklama/Alt Başlık) hücreleri tablo genişliği kadar (A1:X1 / A3:X3) birleştirilmeli ve wrap_text=False olmalıdır. Metinlerin tek sütuna sıkışıp dikey kırılması kesinlikle yasaktır.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>ZORUNLU</t>
         </is>
@@ -40478,7 +40513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -40490,7 +40525,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="54" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
@@ -41022,7 +41057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -41033,7 +41068,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="55" t="inlineStr">
+      <c r="A1" s="72" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>

--- a/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
+++ b/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
@@ -958,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6862,7 +6862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9846,7 +9846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39689,7 +39689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40486,6 +40486,23 @@
         </is>
       </c>
       <c r="D29" t="inlineStr">
+        <is>
+          <t>ZORUNLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vitrin &amp; Yönetici Grafikleri (Executive Showcase Charts)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PANO (Dashboard) sayfasında en az 2 adet yüksek estetikli dinamik grafik bulunmalıdır: 1) Dönemsel Performans &amp; Trend (Çoklu Sütun Bar Grafiği), 2) Portföy / Risk Dağılımı (Modern İnce Halka - Doughnut Chart, HoleSize=%60). Grafikler Bento Grid simetrisinde B28:G44 ve H28:M44 koordinatlarına oturmalıdır.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>ZORUNLU</t>
         </is>
@@ -40513,7 +40530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -41057,7 +41074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>

--- a/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
+++ b/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
@@ -39689,7 +39689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40503,6 +40503,40 @@
         </is>
       </c>
       <c r="D30" t="inlineStr">
+        <is>
+          <t>ZORUNLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Daimi Otomatik Protokol Senkronizasyonu (SSOT)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Projedeki herhangi bir çalışmada geliştirilen her yeni tasarım standardı, mimari kural, formül motoru veya görsel iyileştirme; kullanıcı talep etmese dahi derhal bu master şablona ve runtime_kernel.py dosyasına işlenmek zorundadır. Bu iki dosya tek ve mutlak anayasadır.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ANAYASAL ZORUNLULUK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>İnfografik Renk Uyumu &amp; Vektör Grafik Standardı</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PANO (Dashboard) ve Rapor sayfalarındaki grafikler ham Excel renkleriyle bırakılamaz. Uluslararası vektörel infografik renk paleti zorunludur: Birincil Hacim=#1B365D (Lacivert), İkincil Maliyet=#D97706 (Amber), Üçüncül Hedef=#059669 (Zümrüt Yeşil), Dağılım=#2563EB (Kraliyet Mavisi). Halka grafiklerde her dilim (DataPoint) bu paletle boyanmalı, delik oranı %60 kilitlenmelidir.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>ZORUNLU</t>
         </is>

--- a/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
+++ b/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
@@ -4671,7 +4671,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="59" t="inlineStr">
         <is>
-          <t>5 Yaşındaki Çocuğa Anlatır Gibi Yalın Finansal Karar Mimarisi &amp; Kurumsal Süreç Sözlüğü</t>
+          <t>Yalın, Sade ve Eksiksiz Finansal Karar Mimarisi &amp; Kullanım Rehberi · Siemens &amp; Enterprise Standartları</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="C7" s="62" t="inlineStr">
         <is>
-          <t>GÜNLÜK DİLLE CEVAP (5 YAŞINDA ÇOCUĞA ANLATIR GİBİ)</t>
+          <t>YALIN KURUMSAL AÇIKLAMA</t>
         </is>
       </c>
       <c r="D7" s="62" t="inlineStr">
@@ -39707,6 +39707,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -40465,7 +40466,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>00_HAKKINDA_VE_REHBER (5 yaşındaki çocuğa anlatır gibi sistem sözlüğü), kart içi sıfır gridline/artık border, simetrik dış çerçeve ve altın oran sütun genişlikleri zorunludur.</t>
+          <t>00_HAKKINDA_VE_REHBER (en üst düzey yalınlıkta sistem sözlüğü ve rehberi), kart içi sıfır gridline/artık border, simetrik dış çerçeve ve altın oran sütun genişlikleri zorunludur.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">

--- a/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
+++ b/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
@@ -39689,7 +39689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39707,7 +39707,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -40538,6 +40537,23 @@
         </is>
       </c>
       <c r="D32" t="inlineStr">
+        <is>
+          <t>ZORUNLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Grafik Tuval İzolasyonu &amp; Sıfır Ezilme/Sürtünme</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Grafik nesneleri asla arkasındaki hücreleri ezemez; altına gelen satırlar boş tuval olarak ayrılmalıdır. Grafik içi etiket ve lejantlar dilimlerle çakışmayacak konumlara (Bar: Üst, Halka: Sağ) yerleştirilmeli; tablolardaki sütunlar '###' veya rakam kesilmesine karşı en az +4.5 tampon paya sahip olmalıdır.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>ZORUNLU</t>
         </is>

--- a/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
+++ b/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
@@ -39689,7 +39689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40554,6 +40554,23 @@
         </is>
       </c>
       <c r="D33" t="inlineStr">
+        <is>
+          <t>ZORUNLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sıfır Başlık-Lejant Çakışması &amp; Kılavuz Tablo Genişlik Standardı</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Grafik lejantları başlığı ezmemesi için daima sağda (r) yer almalıdır. Halka grafiklerde dilim içi metin yığılması yasaktır. Kılavuz süreç tablolarında kolonlar metinleri 'SİSTEM KURU' gibi kesmeyecek biçimde en az 30 karakter genişlikte olmalıdır.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>ZORUNLU</t>
         </is>

--- a/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
+++ b/calisma_prorokolu/EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART_UI_LOCKED.xlsx
@@ -39689,7 +39689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40573,6 +40573,23 @@
       <c r="D34" t="inlineStr">
         <is>
           <t>ZORUNLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>OpenXML Evrensel Formül Sözleşmesi &amp; Sıfır #AD? Hatası</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tüm hücre formülleri evrensel İngilizce fonksiyonlar (SUM, IF, ROUND, VLOOKUP) ve virgül (,) parametre ayracı ile yazılmalıdır. Türkçe fonksiyon adları veya noktalı virgül (;) kullanımından kaynaklanan #AD? (#NAME?) hataları kesinlikle yasaktır.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ZORUNLU (SSOT)</t>
         </is>
       </c>
     </row>
